--- a/MZE_Observations_and_Actions_Tracker.xlsx
+++ b/MZE_Observations_and_Actions_Tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://switch21ae.sharepoint.com/sites/Switch21/Shared Documents/Consulting/Belgrade Expo 2027 Phase 2/Consulting/10 SHARED/Operations/Model Zone Exercise (MZE)/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://crowdedevents.sharepoint.com/Consultancy Projects/2026/2. Belgrade 2027/Readiness/11. Model Zone Exercise/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8BED85D-0679-4366-929C-1C3E7B6C4ECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{A8BED85D-0679-4366-929C-1C3E7B6C4ECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1096BB0-3E71-4086-B95D-2649E2671B96}"/>
   <bookViews>
-    <workbookView xWindow="2265" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Legend &amp; Guide" sheetId="1" r:id="rId1"/>
@@ -3480,7 +3480,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3890,13 +3890,13 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4342,19 +4342,19 @@
     <tabColor rgb="FF0D0C4E"/>
   </sheetPr>
   <dimension ref="B2:C18"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="17.25" customHeight="1">
+    <row r="2" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B2" s="10" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:3" ht="36" customHeight="1">
+    <row r="4" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="30" t="s">
         <v>1</v>
       </c>
@@ -4362,7 +4362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="36" customHeight="1">
+    <row r="5" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="30" t="s">
         <v>3</v>
       </c>
@@ -4370,7 +4370,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:3" ht="54" customHeight="1">
+    <row r="6" spans="2:3" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="30" t="s">
         <v>5</v>
       </c>
@@ -4378,7 +4378,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="2:3" ht="31.5" customHeight="1">
+    <row r="7" spans="2:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="30" t="s">
         <v>7</v>
       </c>
@@ -4386,7 +4386,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="2:3" ht="31.5" customHeight="1">
+    <row r="8" spans="2:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="30" t="s">
         <v>9</v>
       </c>
@@ -4394,7 +4394,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:3" ht="54" customHeight="1">
+    <row r="9" spans="2:3" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="30" t="s">
         <v>11</v>
       </c>
@@ -4402,15 +4402,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="2:3">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B10" s="31"/>
     </row>
-    <row r="12" spans="2:3" ht="15" customHeight="1">
+    <row r="12" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B12" s="17" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="2:3" ht="15" customHeight="1">
+    <row r="13" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B13" s="18" t="s">
         <v>14</v>
       </c>
@@ -4418,7 +4418,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="2:3" ht="15" customHeight="1">
+    <row r="14" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B14" s="20" t="s">
         <v>16</v>
       </c>
@@ -4426,7 +4426,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="2:3" ht="15" customHeight="1">
+    <row r="15" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B15" s="21" t="s">
         <v>18</v>
       </c>
@@ -4434,7 +4434,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="2:3" ht="15" customHeight="1">
+    <row r="16" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B16" s="22" t="s">
         <v>20</v>
       </c>
@@ -4442,7 +4442,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="15" customHeight="1">
+    <row r="17" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B17" s="23" t="s">
         <v>22</v>
       </c>
@@ -4450,7 +4450,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:3">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" s="32" t="s">
         <v>24</v>
       </c>
@@ -4468,7 +4468,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I314"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -4477,49 +4477,49 @@
     <col min="5" max="6" width="30" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="34" customWidth="1"/>
-    <col min="9" max="9" width="15.28515625" style="29" customWidth="1"/>
+    <col min="9" max="9" width="15.33203125" style="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="27.6" customHeight="1">
+    <row r="1" spans="1:9" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="24"/>
       <c r="B1" s="24"/>
       <c r="C1" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="55"/>
-    </row>
-    <row r="2" spans="1:9" ht="18" customHeight="1">
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="56"/>
+    </row>
+    <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="24"/>
       <c r="B2" s="24"/>
-      <c r="C2" s="56" t="s">
+      <c r="C2" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="55"/>
-    </row>
-    <row r="3" spans="1:9" ht="18" customHeight="1">
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="56"/>
+    </row>
+    <row r="3" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24"/>
       <c r="B3" s="24"/>
-      <c r="C3" s="56" t="s">
+      <c r="C3" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="55"/>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="56"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -4530,7 +4530,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="25"/>
     </row>
-    <row r="5" spans="1:9" ht="54" customHeight="1">
+    <row r="5" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -4559,7 +4559,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="48.6" customHeight="1">
+    <row r="6" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>33</v>
       </c>
@@ -4580,11 +4580,11 @@
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
-      <c r="I6" s="26" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="32.450000000000003" customHeight="1">
+      <c r="I6" s="27" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>39</v>
       </c>
@@ -4609,7 +4609,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="48.6" customHeight="1">
+    <row r="8" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>42</v>
       </c>
@@ -4634,7 +4634,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="48.6" customHeight="1">
+    <row r="9" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>47</v>
       </c>
@@ -4661,7 +4661,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="48.6" customHeight="1">
+    <row r="10" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>50</v>
       </c>
@@ -4686,7 +4686,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="11" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>54</v>
       </c>
@@ -4713,7 +4713,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="12" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>59</v>
       </c>
@@ -4740,7 +4740,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="13" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>63</v>
       </c>
@@ -4767,7 +4767,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="14" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>66</v>
       </c>
@@ -4794,7 +4794,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="48.6" customHeight="1">
+    <row r="15" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>69</v>
       </c>
@@ -4821,7 +4821,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="48.6" customHeight="1">
+    <row r="16" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>73</v>
       </c>
@@ -4848,7 +4848,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="48.6" customHeight="1">
+    <row r="17" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>78</v>
       </c>
@@ -4875,7 +4875,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="18" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>81</v>
       </c>
@@ -4902,7 +4902,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="42.6" customHeight="1">
+    <row r="19" spans="1:9" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>85</v>
       </c>
@@ -4929,7 +4929,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="20" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>90</v>
       </c>
@@ -4954,7 +4954,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="21" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>93</v>
       </c>
@@ -4981,7 +4981,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="48.6" customHeight="1">
+    <row r="22" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>98</v>
       </c>
@@ -5008,7 +5008,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="23" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>103</v>
       </c>
@@ -5035,7 +5035,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="24" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>106</v>
       </c>
@@ -5060,7 +5060,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="48.6" customHeight="1">
+    <row r="25" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>110</v>
       </c>
@@ -5087,7 +5087,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="26" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>115</v>
       </c>
@@ -5114,7 +5114,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="48.6">
+    <row r="27" spans="1:9" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>119</v>
       </c>
@@ -5139,7 +5139,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="28" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>121</v>
       </c>
@@ -5166,7 +5166,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="48.6" customHeight="1">
+    <row r="29" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>124</v>
       </c>
@@ -5193,7 +5193,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="97.15" customHeight="1">
+    <row r="30" spans="1:9" ht="97.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>129</v>
       </c>
@@ -5218,7 +5218,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="31" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>133</v>
       </c>
@@ -5245,7 +5245,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="48.6" customHeight="1">
+    <row r="32" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>136</v>
       </c>
@@ -5270,7 +5270,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="48.6" customHeight="1">
+    <row r="33" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>139</v>
       </c>
@@ -5297,7 +5297,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="48.6" customHeight="1">
+    <row r="34" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="45" t="s">
         <v>142</v>
       </c>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="I34" s="47"/>
     </row>
-    <row r="35" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="35" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>147</v>
       </c>
@@ -5347,7 +5347,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="16.149999999999999" customHeight="1">
+    <row r="36" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>152</v>
       </c>
@@ -5374,7 +5374,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="37" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>155</v>
       </c>
@@ -5399,7 +5399,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="38" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>158</v>
       </c>
@@ -5426,7 +5426,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="39" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>162</v>
       </c>
@@ -5453,7 +5453,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="16.149999999999999" customHeight="1">
+    <row r="40" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>166</v>
       </c>
@@ -5480,7 +5480,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="41" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>169</v>
       </c>
@@ -5505,7 +5505,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="42" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>171</v>
       </c>
@@ -5532,7 +5532,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="43" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>176</v>
       </c>
@@ -5559,7 +5559,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="24.6" customHeight="1">
+    <row r="44" spans="1:9" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>182</v>
       </c>
@@ -5586,7 +5586,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="45" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>187</v>
       </c>
@@ -5613,7 +5613,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="46" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="45" t="s">
         <v>192</v>
       </c>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="I46" s="47"/>
     </row>
-    <row r="47" spans="1:9" ht="48.6" customHeight="1">
+    <row r="47" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>197</v>
       </c>
@@ -5663,7 +5663,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="48" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>201</v>
       </c>
@@ -5688,7 +5688,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="49" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>203</v>
       </c>
@@ -5713,7 +5713,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="48.6" customHeight="1">
+    <row r="50" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>206</v>
       </c>
@@ -5740,7 +5740,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="16.149999999999999" customHeight="1">
+    <row r="51" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>211</v>
       </c>
@@ -5765,7 +5765,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="52" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>213</v>
       </c>
@@ -5792,7 +5792,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="48.6" customHeight="1">
+    <row r="53" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>218</v>
       </c>
@@ -5819,7 +5819,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="54" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>221</v>
       </c>
@@ -5846,7 +5846,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="55" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>224</v>
       </c>
@@ -5871,7 +5871,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="48.6" customHeight="1">
+    <row r="56" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>227</v>
       </c>
@@ -5898,7 +5898,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="57" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>232</v>
       </c>
@@ -5925,7 +5925,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="58" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>237</v>
       </c>
@@ -5952,7 +5952,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="48.6" customHeight="1">
+    <row r="59" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>241</v>
       </c>
@@ -5979,7 +5979,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="60" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>246</v>
       </c>
@@ -6004,7 +6004,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="48.6" customHeight="1">
+    <row r="61" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>250</v>
       </c>
@@ -6029,7 +6029,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="48.6" customHeight="1">
+    <row r="62" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>254</v>
       </c>
@@ -6056,7 +6056,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="63" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>257</v>
       </c>
@@ -6083,7 +6083,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="64" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>261</v>
       </c>
@@ -6110,7 +6110,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="65" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>267</v>
       </c>
@@ -6137,7 +6137,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="48.6" customHeight="1">
+    <row r="66" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>271</v>
       </c>
@@ -6164,7 +6164,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="67" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>276</v>
       </c>
@@ -6191,7 +6191,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="68" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>281</v>
       </c>
@@ -6218,7 +6218,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="69" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>283</v>
       </c>
@@ -6243,7 +6243,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="70" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>286</v>
       </c>
@@ -6268,7 +6268,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="48.6" customHeight="1">
+    <row r="71" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>290</v>
       </c>
@@ -6293,7 +6293,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="72" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>294</v>
       </c>
@@ -6318,7 +6318,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="73" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>298</v>
       </c>
@@ -6343,7 +6343,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="74" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>302</v>
       </c>
@@ -6368,7 +6368,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="75" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>305</v>
       </c>
@@ -6393,7 +6393,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="76" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>308</v>
       </c>
@@ -6418,7 +6418,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="77" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>311</v>
       </c>
@@ -6443,7 +6443,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="78" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>313</v>
       </c>
@@ -6468,7 +6468,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="79" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>317</v>
       </c>
@@ -6493,7 +6493,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="80" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>320</v>
       </c>
@@ -6518,7 +6518,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="48.6" customHeight="1">
+    <row r="81" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>322</v>
       </c>
@@ -6543,7 +6543,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="82" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>327</v>
       </c>
@@ -6568,7 +6568,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="48.6" customHeight="1">
+    <row r="83" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>331</v>
       </c>
@@ -6595,7 +6595,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="48.6" customHeight="1">
+    <row r="84" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>336</v>
       </c>
@@ -6622,7 +6622,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="48.6" customHeight="1">
+    <row r="85" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>341</v>
       </c>
@@ -6647,7 +6647,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="48.6" customHeight="1">
+    <row r="86" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>345</v>
       </c>
@@ -6674,7 +6674,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="47.45" customHeight="1">
+    <row r="87" spans="1:9" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>350</v>
       </c>
@@ -6701,7 +6701,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="48.6" customHeight="1">
+    <row r="88" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>355</v>
       </c>
@@ -6728,7 +6728,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="89" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>360</v>
       </c>
@@ -6753,7 +6753,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="48.6" customHeight="1">
+    <row r="90" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>364</v>
       </c>
@@ -6778,7 +6778,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="91" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>366</v>
       </c>
@@ -6803,7 +6803,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="92" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>369</v>
       </c>
@@ -6828,7 +6828,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="93" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>372</v>
       </c>
@@ -6853,7 +6853,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="48.6" customHeight="1">
+    <row r="94" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>376</v>
       </c>
@@ -6878,7 +6878,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="48.6" customHeight="1">
+    <row r="95" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>379</v>
       </c>
@@ -6905,7 +6905,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="81" customHeight="1">
+    <row r="96" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>384</v>
       </c>
@@ -6930,7 +6930,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="48.6" customHeight="1">
+    <row r="97" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>387</v>
       </c>
@@ -6955,7 +6955,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="48.6" customHeight="1">
+    <row r="98" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>391</v>
       </c>
@@ -6982,7 +6982,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="99" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>394</v>
       </c>
@@ -7009,7 +7009,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="100" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>397</v>
       </c>
@@ -7034,7 +7034,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="30.6" customHeight="1">
+    <row r="101" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>401</v>
       </c>
@@ -7061,7 +7061,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="48.6" customHeight="1">
+    <row r="102" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>404</v>
       </c>
@@ -7088,7 +7088,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="103" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
         <v>408</v>
       </c>
@@ -7115,7 +7115,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="81" customHeight="1">
+    <row r="104" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
         <v>413</v>
       </c>
@@ -7142,7 +7142,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="48.6" customHeight="1">
+    <row r="105" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
         <v>418</v>
       </c>
@@ -7169,7 +7169,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="106" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
         <v>421</v>
       </c>
@@ -7196,7 +7196,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="107" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
         <v>425</v>
       </c>
@@ -7223,7 +7223,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="48.6" customHeight="1">
+    <row r="108" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>431</v>
       </c>
@@ -7248,7 +7248,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="109" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>433</v>
       </c>
@@ -7273,7 +7273,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="40.15" customHeight="1">
+    <row r="110" spans="1:9" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
         <v>437</v>
       </c>
@@ -7298,7 +7298,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="111" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
         <v>441</v>
       </c>
@@ -7323,7 +7323,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="112" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
         <v>444</v>
       </c>
@@ -7348,7 +7348,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="113" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
         <v>447</v>
       </c>
@@ -7373,7 +7373,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="48.6" customHeight="1">
+    <row r="114" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
         <v>451</v>
       </c>
@@ -7398,7 +7398,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="24.6" customHeight="1">
+    <row r="115" spans="1:9" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
         <v>455</v>
       </c>
@@ -7425,7 +7425,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="116" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
         <v>460</v>
       </c>
@@ -7452,7 +7452,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="117" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
         <v>463</v>
       </c>
@@ -7479,7 +7479,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="48.6" customHeight="1">
+    <row r="118" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
         <v>468</v>
       </c>
@@ -7506,7 +7506,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="48.6" customHeight="1">
+    <row r="119" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
         <v>471</v>
       </c>
@@ -7531,7 +7531,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="120" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
         <v>473</v>
       </c>
@@ -7558,7 +7558,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="121" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
         <v>477</v>
       </c>
@@ -7583,7 +7583,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="48.6" customHeight="1">
+    <row r="122" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
         <v>481</v>
       </c>
@@ -7610,7 +7610,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="48.6" customHeight="1">
+    <row r="123" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
         <v>486</v>
       </c>
@@ -7635,7 +7635,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="48.6" customHeight="1">
+    <row r="124" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
         <v>489</v>
       </c>
@@ -7660,7 +7660,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="48.6" customHeight="1">
+    <row r="125" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
         <v>491</v>
       </c>
@@ -7685,7 +7685,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="126" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
         <v>494</v>
       </c>
@@ -7710,7 +7710,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="127" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
         <v>497</v>
       </c>
@@ -7735,7 +7735,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="48.6" customHeight="1">
+    <row r="128" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
         <v>501</v>
       </c>
@@ -7760,7 +7760,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="48.6" customHeight="1">
+    <row r="129" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
         <v>505</v>
       </c>
@@ -7787,7 +7787,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="48.6" customHeight="1">
+    <row r="130" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
         <v>509</v>
       </c>
@@ -7812,7 +7812,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="131" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
         <v>514</v>
       </c>
@@ -7837,7 +7837,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="48.6" customHeight="1">
+    <row r="132" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
         <v>518</v>
       </c>
@@ -7862,7 +7862,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="48.6" customHeight="1">
+    <row r="133" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>520</v>
       </c>
@@ -7887,7 +7887,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="134" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
         <v>524</v>
       </c>
@@ -7912,7 +7912,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="135" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>528</v>
       </c>
@@ -7937,7 +7937,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="48.6" customHeight="1">
+    <row r="136" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
         <v>531</v>
       </c>
@@ -7962,7 +7962,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="48.6" customHeight="1">
+    <row r="137" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
         <v>534</v>
       </c>
@@ -7987,7 +7987,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="81" customHeight="1">
+    <row r="138" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
         <v>536</v>
       </c>
@@ -8012,7 +8012,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="139" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>540</v>
       </c>
@@ -8037,7 +8037,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="140" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
         <v>544</v>
       </c>
@@ -8062,7 +8062,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="141" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
         <v>549</v>
       </c>
@@ -8087,7 +8087,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="142" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
         <v>553</v>
       </c>
@@ -8112,7 +8112,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="48.6" customHeight="1">
+    <row r="143" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
         <v>556</v>
       </c>
@@ -8137,7 +8137,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="144" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
         <v>560</v>
       </c>
@@ -8162,7 +8162,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="48.6" customHeight="1">
+    <row r="145" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
         <v>563</v>
       </c>
@@ -8187,7 +8187,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="146" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
         <v>566</v>
       </c>
@@ -8212,7 +8212,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="48.6" customHeight="1">
+    <row r="147" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
         <v>570</v>
       </c>
@@ -8237,7 +8237,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="48.6" customHeight="1">
+    <row r="148" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
         <v>574</v>
       </c>
@@ -8262,7 +8262,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="149" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
         <v>579</v>
       </c>
@@ -8287,7 +8287,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="150" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
         <v>583</v>
       </c>
@@ -8312,7 +8312,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="48.6" customHeight="1">
+    <row r="151" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
         <v>586</v>
       </c>
@@ -8337,7 +8337,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="48.6" customHeight="1">
+    <row r="152" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
         <v>590</v>
       </c>
@@ -8362,7 +8362,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="48.6" customHeight="1">
+    <row r="153" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
         <v>594</v>
       </c>
@@ -8387,7 +8387,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="154" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
         <v>598</v>
       </c>
@@ -8412,7 +8412,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="48.6" customHeight="1">
+    <row r="155" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
         <v>603</v>
       </c>
@@ -8439,7 +8439,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="156" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
         <v>607</v>
       </c>
@@ -8464,7 +8464,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="48.6" customHeight="1">
+    <row r="157" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
         <v>610</v>
       </c>
@@ -8489,7 +8489,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="145.9" customHeight="1">
+    <row r="158" spans="1:9" ht="145.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
         <v>612</v>
       </c>
@@ -8514,7 +8514,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="48.6" customHeight="1">
+    <row r="159" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
         <v>616</v>
       </c>
@@ -8539,7 +8539,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="48.6" customHeight="1">
+    <row r="160" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="s">
         <v>619</v>
       </c>
@@ -8566,7 +8566,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="48.6" customHeight="1">
+    <row r="161" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
         <v>623</v>
       </c>
@@ -8593,7 +8593,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="162" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
         <v>627</v>
       </c>
@@ -8620,7 +8620,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="163" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
         <v>630</v>
       </c>
@@ -8647,7 +8647,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="164" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
         <v>633</v>
       </c>
@@ -8674,7 +8674,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="48.6" customHeight="1">
+    <row r="165" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
         <v>636</v>
       </c>
@@ -8699,7 +8699,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="48.6" customHeight="1">
+    <row r="166" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
         <v>639</v>
       </c>
@@ -8726,7 +8726,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="48.6" customHeight="1">
+    <row r="167" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
         <v>643</v>
       </c>
@@ -8751,7 +8751,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="113.45" customHeight="1">
+    <row r="168" spans="1:9" ht="113.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
         <v>646</v>
       </c>
@@ -8778,7 +8778,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="81" customHeight="1">
+    <row r="169" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
         <v>649</v>
       </c>
@@ -8803,7 +8803,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="97.15" customHeight="1">
+    <row r="170" spans="1:9" ht="97.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
         <v>651</v>
       </c>
@@ -8828,7 +8828,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="97.15" customHeight="1">
+    <row r="171" spans="1:9" ht="97.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
         <v>654</v>
       </c>
@@ -8853,7 +8853,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="172" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
         <v>658</v>
       </c>
@@ -8878,7 +8878,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="173" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
         <v>662</v>
       </c>
@@ -8903,7 +8903,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="81" customHeight="1">
+    <row r="174" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
         <v>665</v>
       </c>
@@ -8928,7 +8928,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="113.45" customHeight="1">
+    <row r="175" spans="1:9" ht="113.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
         <v>667</v>
       </c>
@@ -8955,7 +8955,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="48.6" customHeight="1">
+    <row r="176" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="s">
         <v>671</v>
       </c>
@@ -8980,7 +8980,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="177" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
         <v>674</v>
       </c>
@@ -9005,7 +9005,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="48.6" customHeight="1">
+    <row r="178" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
         <v>678</v>
       </c>
@@ -9030,7 +9030,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="179" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
         <v>680</v>
       </c>
@@ -9055,7 +9055,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="48.6" customHeight="1">
+    <row r="180" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
         <v>684</v>
       </c>
@@ -9080,7 +9080,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="48.6" customHeight="1">
+    <row r="181" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
         <v>687</v>
       </c>
@@ -9105,7 +9105,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="48.6" customHeight="1">
+    <row r="182" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
         <v>690</v>
       </c>
@@ -9130,7 +9130,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="81" customHeight="1">
+    <row r="183" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
         <v>694</v>
       </c>
@@ -9155,7 +9155,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="48.6" customHeight="1">
+    <row r="184" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
         <v>697</v>
       </c>
@@ -9182,7 +9182,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="48.6" customHeight="1">
+    <row r="185" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
         <v>700</v>
       </c>
@@ -9207,7 +9207,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="186" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
         <v>703</v>
       </c>
@@ -9232,7 +9232,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="187" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
         <v>707</v>
       </c>
@@ -9257,7 +9257,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="188" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
         <v>709</v>
       </c>
@@ -9282,7 +9282,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="48.6" customHeight="1">
+    <row r="189" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
         <v>712</v>
       </c>
@@ -9307,7 +9307,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="48.6" customHeight="1">
+    <row r="190" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
         <v>714</v>
       </c>
@@ -9334,7 +9334,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="48.6" customHeight="1">
+    <row r="191" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
         <v>719</v>
       </c>
@@ -9359,7 +9359,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="192" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
         <v>722</v>
       </c>
@@ -9384,7 +9384,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="193" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
         <v>725</v>
       </c>
@@ -9409,7 +9409,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="81" customHeight="1">
+    <row r="194" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
         <v>729</v>
       </c>
@@ -9434,7 +9434,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="48.6" customHeight="1">
+    <row r="195" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
         <v>731</v>
       </c>
@@ -9459,7 +9459,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="196" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
         <v>733</v>
       </c>
@@ -9484,7 +9484,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="48.6" customHeight="1">
+    <row r="197" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
         <v>735</v>
       </c>
@@ -9509,7 +9509,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="48.6" customHeight="1">
+    <row r="198" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="s">
         <v>737</v>
       </c>
@@ -9536,7 +9536,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="199" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
         <v>742</v>
       </c>
@@ -9561,7 +9561,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="97.15" customHeight="1">
+    <row r="200" spans="1:9" ht="97.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
         <v>745</v>
       </c>
@@ -9586,7 +9586,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="48.6" customHeight="1">
+    <row r="201" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
         <v>749</v>
       </c>
@@ -9613,7 +9613,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="48.6" customHeight="1">
+    <row r="202" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
         <v>753</v>
       </c>
@@ -9638,7 +9638,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="81" customHeight="1">
+    <row r="203" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
         <v>756</v>
       </c>
@@ -9663,7 +9663,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="48.6" customHeight="1">
+    <row r="204" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
         <v>760</v>
       </c>
@@ -9688,7 +9688,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="205" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
         <v>764</v>
       </c>
@@ -9715,7 +9715,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="206" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="s">
         <v>767</v>
       </c>
@@ -9740,7 +9740,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="207" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
         <v>769</v>
       </c>
@@ -9765,7 +9765,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="48.6" customHeight="1">
+    <row r="208" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
         <v>771</v>
       </c>
@@ -9790,7 +9790,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="209" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
         <v>773</v>
       </c>
@@ -9815,7 +9815,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="210" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
         <v>775</v>
       </c>
@@ -9840,7 +9840,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="81" customHeight="1">
+    <row r="211" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
         <v>778</v>
       </c>
@@ -9865,7 +9865,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="81" customHeight="1">
+    <row r="212" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
         <v>782</v>
       </c>
@@ -9890,7 +9890,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="81" customHeight="1">
+    <row r="213" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
         <v>784</v>
       </c>
@@ -9915,7 +9915,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="81" customHeight="1">
+    <row r="214" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="3" t="s">
         <v>788</v>
       </c>
@@ -9940,7 +9940,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="81" customHeight="1">
+    <row r="215" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
         <v>792</v>
       </c>
@@ -9965,7 +9965,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="48.6" customHeight="1">
+    <row r="216" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="3" t="s">
         <v>794</v>
       </c>
@@ -9990,7 +9990,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="16.149999999999999" customHeight="1">
+    <row r="217" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
         <v>798</v>
       </c>
@@ -10015,7 +10015,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="81" customHeight="1">
+    <row r="218" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
         <v>800</v>
       </c>
@@ -10040,7 +10040,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="81" customHeight="1">
+    <row r="219" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
         <v>802</v>
       </c>
@@ -10067,7 +10067,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="81" customHeight="1">
+    <row r="220" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="3" t="s">
         <v>806</v>
       </c>
@@ -10094,7 +10094,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="48.6" customHeight="1">
+    <row r="221" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
         <v>809</v>
       </c>
@@ -10119,7 +10119,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="48.6" customHeight="1">
+    <row r="222" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
         <v>813</v>
       </c>
@@ -10144,7 +10144,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="48.6" customHeight="1">
+    <row r="223" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
         <v>815</v>
       </c>
@@ -10169,7 +10169,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="97.15" customHeight="1">
+    <row r="224" spans="1:9" ht="97.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
         <v>817</v>
       </c>
@@ -10194,7 +10194,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="225" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
         <v>822</v>
       </c>
@@ -10219,7 +10219,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="226" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="3" t="s">
         <v>826</v>
       </c>
@@ -10246,7 +10246,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="48.6" customHeight="1">
+    <row r="227" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
         <v>830</v>
       </c>
@@ -10273,7 +10273,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="97.15" customHeight="1">
+    <row r="228" spans="1:9" ht="97.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
         <v>833</v>
       </c>
@@ -10298,7 +10298,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="229" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
         <v>837</v>
       </c>
@@ -10323,7 +10323,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="81" customHeight="1">
+    <row r="230" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
         <v>840</v>
       </c>
@@ -10348,7 +10348,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="81" customHeight="1">
+    <row r="231" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
         <v>843</v>
       </c>
@@ -10373,7 +10373,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="81" customHeight="1">
+    <row r="232" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="3" t="s">
         <v>846</v>
       </c>
@@ -10400,7 +10400,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="48.6" customHeight="1">
+    <row r="233" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
         <v>849</v>
       </c>
@@ -10425,7 +10425,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="81" customHeight="1">
+    <row r="234" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="3" t="s">
         <v>853</v>
       </c>
@@ -10450,7 +10450,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="235" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
         <v>855</v>
       </c>
@@ -10475,7 +10475,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="48.6" customHeight="1">
+    <row r="236" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="3" t="s">
         <v>858</v>
       </c>
@@ -10502,7 +10502,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="237" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
         <v>863</v>
       </c>
@@ -10527,7 +10527,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="81" customHeight="1">
+    <row r="238" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="3" t="s">
         <v>866</v>
       </c>
@@ -10552,7 +10552,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="81" customHeight="1">
+    <row r="239" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
         <v>870</v>
       </c>
@@ -10577,7 +10577,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="240" spans="1:9" ht="81" customHeight="1">
+    <row r="240" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="3" t="s">
         <v>873</v>
       </c>
@@ -10602,7 +10602,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="241" spans="1:9" ht="81" customHeight="1">
+    <row r="241" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
         <v>877</v>
       </c>
@@ -10627,7 +10627,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="242" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="242" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="3" t="s">
         <v>881</v>
       </c>
@@ -10652,7 +10652,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="243" spans="1:9" ht="81" customHeight="1">
+    <row r="243" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
         <v>883</v>
       </c>
@@ -10677,7 +10677,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="244" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="3" t="s">
         <v>886</v>
       </c>
@@ -10702,7 +10702,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="81" customHeight="1">
+    <row r="245" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
         <v>888</v>
       </c>
@@ -10727,7 +10727,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="246" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="246" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="3" t="s">
         <v>890</v>
       </c>
@@ -10752,7 +10752,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="48.6" customHeight="1">
+    <row r="247" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
         <v>895</v>
       </c>
@@ -10777,7 +10777,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="248" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="3" t="s">
         <v>897</v>
       </c>
@@ -10802,7 +10802,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="97.15" customHeight="1">
+    <row r="249" spans="1:9" ht="97.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
         <v>900</v>
       </c>
@@ -10827,7 +10827,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="250" spans="1:9" ht="48.6" customHeight="1">
+    <row r="250" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="3" t="s">
         <v>904</v>
       </c>
@@ -10852,7 +10852,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="48.6" customHeight="1">
+    <row r="251" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
         <v>907</v>
       </c>
@@ -10879,7 +10879,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="48.6" customHeight="1">
+    <row r="252" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="3" t="s">
         <v>912</v>
       </c>
@@ -10906,7 +10906,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="97.15" customHeight="1">
+    <row r="253" spans="1:9" ht="97.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="3" t="s">
         <v>918</v>
       </c>
@@ -10931,7 +10931,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="254" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="3" t="s">
         <v>922</v>
       </c>
@@ -10956,7 +10956,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="81" customHeight="1">
+    <row r="255" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="3" t="s">
         <v>924</v>
       </c>
@@ -10981,7 +10981,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="256" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="3" t="s">
         <v>928</v>
       </c>
@@ -11006,7 +11006,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="257" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="257" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="3" t="s">
         <v>933</v>
       </c>
@@ -11031,7 +11031,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="48.6" customHeight="1">
+    <row r="258" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="3" t="s">
         <v>936</v>
       </c>
@@ -11056,7 +11056,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="259" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="259" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="3" t="s">
         <v>939</v>
       </c>
@@ -11083,7 +11083,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="260" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="260" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="3" t="s">
         <v>944</v>
       </c>
@@ -11108,7 +11108,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="261" spans="1:9" ht="97.15" customHeight="1">
+    <row r="261" spans="1:9" ht="97.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="3" t="s">
         <v>947</v>
       </c>
@@ -11133,7 +11133,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="262" spans="1:9" ht="113.45" customHeight="1">
+    <row r="262" spans="1:9" ht="113.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="3" t="s">
         <v>951</v>
       </c>
@@ -11158,7 +11158,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="263" spans="1:9" ht="48.6" customHeight="1">
+    <row r="263" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="3" t="s">
         <v>956</v>
       </c>
@@ -11185,7 +11185,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="81" customHeight="1">
+    <row r="264" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="3" t="s">
         <v>960</v>
       </c>
@@ -11210,7 +11210,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="265" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="265" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="3" t="s">
         <v>965</v>
       </c>
@@ -11235,7 +11235,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="266" spans="1:9" ht="48.6" customHeight="1">
+    <row r="266" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="3" t="s">
         <v>967</v>
       </c>
@@ -11260,7 +11260,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="267" spans="1:9" ht="81" customHeight="1">
+    <row r="267" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="3" t="s">
         <v>969</v>
       </c>
@@ -11285,7 +11285,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="268" spans="1:9" ht="81" customHeight="1">
+    <row r="268" spans="1:9" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="3" t="s">
         <v>972</v>
       </c>
@@ -11310,7 +11310,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="269" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="269" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="3" t="s">
         <v>974</v>
       </c>
@@ -11335,7 +11335,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="270" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="270" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="3" t="s">
         <v>977</v>
       </c>
@@ -11360,7 +11360,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="271" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="271" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="34" t="s">
         <v>980</v>
       </c>
@@ -11387,7 +11387,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="272" spans="1:9" ht="48.6" customHeight="1">
+    <row r="272" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="34" t="s">
         <v>984</v>
       </c>
@@ -11412,7 +11412,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="273" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="273" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="34" t="s">
         <v>987</v>
       </c>
@@ -11437,7 +11437,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="274" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="274" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="34" t="s">
         <v>990</v>
       </c>
@@ -11464,7 +11464,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="275" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="275" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="34" t="s">
         <v>995</v>
       </c>
@@ -11489,7 +11489,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="276" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="276" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="34" t="s">
         <v>998</v>
       </c>
@@ -11516,7 +11516,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="277" spans="1:9" ht="48.6" customHeight="1">
+    <row r="277" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="34" t="s">
         <v>1001</v>
       </c>
@@ -11541,7 +11541,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="278" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="278" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="34" t="s">
         <v>1006</v>
       </c>
@@ -11566,7 +11566,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="279" spans="1:9" ht="48.6" customHeight="1">
+    <row r="279" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="34" t="s">
         <v>1009</v>
       </c>
@@ -11591,7 +11591,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="280" spans="1:9" ht="48.6" customHeight="1">
+    <row r="280" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="34" t="s">
         <v>1013</v>
       </c>
@@ -11618,7 +11618,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="281" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="281" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="34" t="s">
         <v>1017</v>
       </c>
@@ -11645,7 +11645,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="282" spans="1:9" ht="48.6" customHeight="1">
+    <row r="282" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="34" t="s">
         <v>1022</v>
       </c>
@@ -11670,7 +11670,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="283" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="283" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="34" t="s">
         <v>1024</v>
       </c>
@@ -11697,7 +11697,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="284" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="284" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="34" t="s">
         <v>1027</v>
       </c>
@@ -11724,7 +11724,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="285" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="285" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="34" t="s">
         <v>1032</v>
       </c>
@@ -11751,7 +11751,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="286" spans="1:9" ht="48.6" customHeight="1">
+    <row r="286" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="34" t="s">
         <v>1037</v>
       </c>
@@ -11776,7 +11776,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="287" spans="1:9" ht="48.6" customHeight="1">
+    <row r="287" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="34" t="s">
         <v>1041</v>
       </c>
@@ -11801,7 +11801,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="288" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="288" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="34" t="s">
         <v>1043</v>
       </c>
@@ -11826,7 +11826,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="289" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="289" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="34" t="s">
         <v>1047</v>
       </c>
@@ -11851,7 +11851,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="290" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="290" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="34" t="s">
         <v>1051</v>
       </c>
@@ -11876,7 +11876,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="291" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="291" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="34" t="s">
         <v>1053</v>
       </c>
@@ -11901,7 +11901,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="292" spans="1:9" ht="48.6" customHeight="1">
+    <row r="292" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="34" t="s">
         <v>1057</v>
       </c>
@@ -11928,7 +11928,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="293" spans="1:9" ht="48.6" customHeight="1">
+    <row r="293" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="34" t="s">
         <v>1061</v>
       </c>
@@ -11953,7 +11953,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="294" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="294" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="34" t="s">
         <v>1064</v>
       </c>
@@ -11978,7 +11978,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="295" spans="1:9" ht="48.6" customHeight="1">
+    <row r="295" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="34" t="s">
         <v>1067</v>
       </c>
@@ -12003,7 +12003,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="296" spans="1:9" ht="48.6" customHeight="1">
+    <row r="296" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="34" t="s">
         <v>1071</v>
       </c>
@@ -12030,7 +12030,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="297" spans="1:9" ht="48.6" customHeight="1">
+    <row r="297" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="34" t="s">
         <v>1076</v>
       </c>
@@ -12057,7 +12057,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="298" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="298" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="34" t="s">
         <v>1080</v>
       </c>
@@ -12082,7 +12082,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="299" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="299" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="34" t="s">
         <v>1084</v>
       </c>
@@ -12107,7 +12107,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="300" spans="1:9" ht="48.6" customHeight="1">
+    <row r="300" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="34" t="s">
         <v>1086</v>
       </c>
@@ -12132,7 +12132,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="301" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="301" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="34" t="s">
         <v>1089</v>
       </c>
@@ -12157,7 +12157,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="302" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="302" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="34" t="s">
         <v>1092</v>
       </c>
@@ -12182,7 +12182,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="303" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="303" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="34" t="s">
         <v>1095</v>
       </c>
@@ -12207,7 +12207,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="304" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="304" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="34" t="s">
         <v>1098</v>
       </c>
@@ -12232,7 +12232,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="305" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="305" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="34" t="s">
         <v>1101</v>
       </c>
@@ -12259,7 +12259,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="306" spans="1:9" ht="97.15" customHeight="1">
+    <row r="306" spans="1:9" ht="97.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="34" t="s">
         <v>1104</v>
       </c>
@@ -12284,7 +12284,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="307" spans="1:9" ht="48.6" customHeight="1">
+    <row r="307" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="34" t="s">
         <v>1108</v>
       </c>
@@ -12309,7 +12309,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="308" spans="1:9" ht="48.6" customHeight="1">
+    <row r="308" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="34" t="s">
         <v>1110</v>
       </c>
@@ -12334,7 +12334,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="309" spans="1:9" ht="48.6" customHeight="1">
+    <row r="309" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="34" t="s">
         <v>1112</v>
       </c>
@@ -12359,7 +12359,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="310" spans="1:9" ht="48.6" customHeight="1">
+    <row r="310" spans="1:9" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="34" t="s">
         <v>1116</v>
       </c>
@@ -12384,7 +12384,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="311" spans="1:9" ht="32.450000000000003" customHeight="1">
+    <row r="311" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="34" t="s">
         <v>1119</v>
       </c>
@@ -12411,7 +12411,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="312" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="312" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="34" t="s">
         <v>1121</v>
       </c>
@@ -12436,7 +12436,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="313" spans="1:9" ht="97.15" customHeight="1">
+    <row r="313" spans="1:9" ht="97.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="34" t="s">
         <v>1125</v>
       </c>
@@ -12461,7 +12461,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="314" spans="1:9" ht="64.900000000000006" customHeight="1">
+    <row r="314" spans="1:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="34" t="s">
         <v>1127</v>
       </c>
@@ -12538,7 +12538,7 @@
     <tabColor rgb="FF0D0C4E"/>
   </sheetPr>
   <dimension ref="B2:G37"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -12548,17 +12548,17 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="17.25" customHeight="1">
+    <row r="2" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B2" s="10" t="s">
         <v>1129</v>
       </c>
     </row>
-    <row r="3" spans="2:7" ht="15" customHeight="1">
+    <row r="3" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B3" s="11" t="s">
         <v>1130</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="15" customHeight="1">
+    <row r="5" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="12" t="s">
         <v>1131</v>
       </c>
@@ -12566,7 +12566,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="15" customHeight="1">
+    <row r="6" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="13" t="s">
         <v>30</v>
       </c>
@@ -12583,7 +12583,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="15" customHeight="1">
+    <row r="7" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B7" s="49" t="s">
         <v>14</v>
       </c>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="D7" s="14">
         <f>COUNTIFS('Action Tracker'!$D$6:$D$387,$B7,'Action Tracker'!$I$6:$I$387,"Open")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="14" t="str">
         <f t="array" ref="F7:F37">_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER('Action Tracker'!F6:F243, 'Action Tracker'!F6:F243&lt;&gt;"")))</f>
@@ -12604,7 +12604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="15" customHeight="1">
+    <row r="8" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B8" s="50" t="s">
         <v>16</v>
       </c>
@@ -12623,7 +12623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:7" ht="15" customHeight="1">
+    <row r="9" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B9" s="51" t="s">
         <v>18</v>
       </c>
@@ -12642,7 +12642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="2:7" ht="15" customHeight="1">
+    <row r="10" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B10" s="52" t="s">
         <v>20</v>
       </c>
@@ -12661,7 +12661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:7" ht="15" customHeight="1">
+    <row r="11" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B11" s="53" t="s">
         <v>22</v>
       </c>
@@ -12680,7 +12680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="15" customHeight="1">
+    <row r="12" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B12" s="15" t="s">
         <v>1136</v>
       </c>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="D12" s="15">
         <f>SUM(D7:D11)</f>
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F12" s="14" t="str">
         <v>C&amp;P Ceremonies Department Operating Plan</v>
@@ -12699,7 +12699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="15" customHeight="1">
+    <row r="13" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
@@ -12710,7 +12710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="15" customHeight="1">
+    <row r="14" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="F14" s="14" t="str">
         <v>C&amp;P Ceremonies Department Operating Plan, Venue Operating Plan, Zone Operating Plan</v>
       </c>
@@ -12718,7 +12718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="15" customHeight="1">
+    <row r="15" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="F15" s="14" t="str">
         <v>C4i ConOps</v>
       </c>
@@ -12726,7 +12726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="15" customHeight="1">
+    <row r="16" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="F16" s="14" t="str">
         <v>Catering Department Operating Plan, Catering Policy &amp; Procedure, Workforce Policy &amp; Procedure, Volunteer Policy &amp; Procedure, Zone Operating Plan</v>
       </c>
@@ -12734,7 +12734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="6:7" ht="15" customHeight="1">
+    <row r="17" spans="6:7" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="F17" s="14" t="str">
         <v>Catering Department Operating Plan, Catering Policy &amp; Procedure, Workforce Policy &amp; Procedure, Zone Operating Plan</v>
       </c>
@@ -12742,7 +12742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="6:7" ht="15" customHeight="1">
+    <row r="18" spans="6:7" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="F18" s="14" t="str">
         <v>CAW Department Operating Plan, Guest Services Department Operating Plan</v>
       </c>
@@ -12750,7 +12750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="6:7" ht="15" customHeight="1">
+    <row r="19" spans="6:7" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="F19" s="14" t="str">
         <v>CAW Department Operating Plan, Zone Operating Plan</v>
       </c>
@@ -12758,7 +12758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="6:7" ht="15" customHeight="1">
+    <row r="20" spans="6:7" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="F20" s="14" t="str">
         <v>Ceremonies Department Operating Plan, Crowd Management Department Operating Plan, Venue Operating Plan, Zone Operating Plan, Expo Site Operating Plan</v>
       </c>
@@ -12766,7 +12766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="6:7" ht="15" customHeight="1">
+    <row r="21" spans="6:7" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="F21" s="14" t="str">
         <v>Ceremonies Department Operating Plan, Protocol Department Operating Plan</v>
       </c>
@@ -12774,7 +12774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="6:7" ht="15" customHeight="1">
+    <row r="22" spans="6:7" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="F22" s="14" t="str">
         <v>Ceremonies Department Operating Plan, Protocol Department Operating Plan, Crowd Management Department Operating Plan, Venue Operating Plan, Zone Operating Plan, Expo Site Operating Plan</v>
       </c>
@@ -12782,7 +12782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="6:7" ht="15" customHeight="1">
+    <row r="23" spans="6:7" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="F23" s="14" t="str">
         <v>Ceremonies Department Operating Plan, Protocol Department Operating Plan, Venue Operating Plan, Zone Operating Plan</v>
       </c>
@@ -12790,7 +12790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="6:7" ht="15" customHeight="1">
+    <row r="24" spans="6:7" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="F24" s="14" t="str">
         <v>Commercial Department Operating Plan, Commercial Policy &amp; Procedure</v>
       </c>
@@ -12798,7 +12798,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="6:7" ht="16.899999999999999" customHeight="1">
+    <row r="25" spans="6:7" ht="16.95" customHeight="1" x14ac:dyDescent="0.5">
       <c r="F25" s="14" t="str">
         <v>Commercial Department Operating Plan, Venue Operating Plan, Zone Operating Plan</v>
       </c>
@@ -12806,7 +12806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="6:7" ht="16.899999999999999" customHeight="1">
+    <row r="26" spans="6:7" ht="16.95" customHeight="1" x14ac:dyDescent="0.5">
       <c r="F26" s="14" t="str">
         <v>Commercial Department Operating Plan, Zone Operating Plan</v>
       </c>
@@ -12814,7 +12814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="6:7" ht="16.899999999999999" customHeight="1">
+    <row r="27" spans="6:7" ht="16.95" customHeight="1" x14ac:dyDescent="0.5">
       <c r="F27" s="14" t="str">
         <v>Commercial Policy &amp; Procedure</v>
       </c>
@@ -12822,7 +12822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="6:7" ht="16.899999999999999" customHeight="1">
+    <row r="28" spans="6:7" ht="16.95" customHeight="1" x14ac:dyDescent="0.5">
       <c r="F28" s="14" t="str">
         <v>Content &amp; Programming Department Operating Plan, Content &amp; Programming Policy &amp; Procedure</v>
       </c>
@@ -12830,7 +12830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="6:7" ht="16.899999999999999" customHeight="1">
+    <row r="29" spans="6:7" ht="16.95" customHeight="1" x14ac:dyDescent="0.5">
       <c r="F29" s="14" t="str">
         <v xml:space="preserve">Content &amp; Programming Department Operating Plan, EMS, Zone Operating Plan, Expo Site Operating Plan, </v>
       </c>
@@ -12838,7 +12838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="6:7" ht="16.899999999999999" customHeight="1">
+    <row r="30" spans="6:7" ht="16.95" customHeight="1" x14ac:dyDescent="0.5">
       <c r="F30" s="14" t="str">
         <v>Crowd Management Department Operating Plan, Crowd Management Policy &amp; Procedure</v>
       </c>
@@ -12846,7 +12846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="6:7" ht="16.899999999999999" customHeight="1">
+    <row r="31" spans="6:7" ht="16.95" customHeight="1" x14ac:dyDescent="0.5">
       <c r="F31" s="14" t="str">
         <v>Crowd Management Department Operating Plan, Crowd Management Policy &amp; Procedure, Zone Operating Plan</v>
       </c>
@@ -12854,7 +12854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="6:7">
+    <row r="32" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F32" t="str">
         <v>Crowd Management Department Operating Plan, Crowd Management Policy &amp; Procedure, Zone Operating Plan, Expo Site Operating Plan, C4i ConOps</v>
       </c>
@@ -12862,7 +12862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="6:7">
+    <row r="33" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F33" t="str">
         <v>Crowd Management Department Operating Plan, Sports Department Operating Plan, Zone Operating Plan</v>
       </c>
@@ -12870,7 +12870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="6:7">
+    <row r="34" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F34" t="str">
         <v>Crowd Management Department Operating Plan, Zone Operating Plan, Expo Site Operating Plan</v>
       </c>
@@ -12878,7 +12878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="6:7">
+    <row r="35" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F35" t="str">
         <v>Crowd Management Operating Plan, Crowd Management Policy &amp; Procedure, Venue Operating Plans, Zone Operating Plan</v>
       </c>
@@ -12886,7 +12886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="6:7">
+    <row r="36" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F36" t="str">
         <v>Cultural, Music &amp; Entertainment Department Operating Plan</v>
       </c>
@@ -12894,7 +12894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="6:7">
+    <row r="37" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F37" t="str">
         <v>Cultural, Music &amp; Entertainment Department Operating Plan, Zone Operating Plan</v>
       </c>
@@ -12909,21 +12909,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="09bcd321-a062-4a38-9f8d-346476dc9f3b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="de465438-1db6-4f0d-ba96-a99ee8a17983" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007633164E1130CC45AC931610B0E4D233" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="361e9005b21777e0eaa8b7f1ad866e8d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="09bcd321-a062-4a38-9f8d-346476dc9f3b" xmlns:ns3="de465438-1db6-4f0d-ba96-a99ee8a17983" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c29794639afa06fd5eacb00a33c687ec" ns2:_="" ns3:_="">
-    <xsd:import namespace="09bcd321-a062-4a38-9f8d-346476dc9f3b"/>
-    <xsd:import namespace="de465438-1db6-4f0d-ba96-a99ee8a17983"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010000E7ACCEC0201D4097C2021E46ECE60A" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cf4a2642e5c99502294ccf1838849ab7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="374220f3-34e9-48c9-8c58-31faa72ff407" xmlns:ns3="1b1ffb37-8927-4fbe-961f-c7a3199710b9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="db22d4e5c9e9253f9efc8049b9c96518" ns2:_="" ns3:_="">
+    <xsd:import namespace="374220f3-34e9-48c9-8c58-31faa72ff407"/>
+    <xsd:import namespace="1b1ffb37-8927-4fbe-961f-c7a3199710b9"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -12933,15 +12931,14 @@
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -12949,7 +12946,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="09bcd321-a062-4a38-9f8d-346476dc9f3b" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="374220f3-34e9-48c9-8c58-31faa72ff407" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -12967,55 +12964,50 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="14" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="899a7c83-cf10-4ea3-9659-ffaf6efe00b0" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="bf540109-29d0-4261-bc1d-7a69fb9ddf0c" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
         </xsd:sequence>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="17" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Unknown"/>
       </xsd:simpleType>
     </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="19" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="de465438-1db6-4f0d-ba96-a99ee8a17983" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1b1ffb37-8927-4fbe-961f-c7a3199710b9" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="15" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{5168df11-3e5c-4b16-a155-975f47481562}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="de465438-1db6-4f0d-ba96-a99ee8a17983">
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{62fab9a7-8f7c-4cd8-93fa-289e163ef8f0}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="1b1ffb37-8927-4fbe-961f-c7a3199710b9">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:MultiChoiceLookup">
@@ -13127,22 +13119,56 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="374220f3-34e9-48c9-8c58-31faa72ff407">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="1b1ffb37-8927-4fbe-961f-c7a3199710b9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{206439E8-84F1-42D1-8C84-9127261BCA0C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F365100B-4C08-4A05-9DDA-C20D05B32AE0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AABAF91-DBDA-447A-93A2-02D49DD515C1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{575A629E-21CC-4AF5-BD8F-A4E6B4B4CA39}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="374220f3-34e9-48c9-8c58-31faa72ff407"/>
+    <ds:schemaRef ds:uri="1b1ffb37-8927-4fbe-961f-c7a3199710b9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F365100B-4C08-4A05-9DDA-C20D05B32AE0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{206439E8-84F1-42D1-8C84-9127261BCA0C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="1b1ffb37-8927-4fbe-961f-c7a3199710b9"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="374220f3-34e9-48c9-8c58-31faa72ff407"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/MZE_Observations_and_Actions_Tracker.xlsx
+++ b/MZE_Observations_and_Actions_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://crowdedevents.sharepoint.com/Consultancy Projects/2026/2. Belgrade 2027/Readiness/11. Model Zone Exercise/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{A8BED85D-0679-4366-929C-1C3E7B6C4ECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1096BB0-3E71-4086-B95D-2649E2671B96}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{A8BED85D-0679-4366-929C-1C3E7B6C4ECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCD24F29-5171-49FD-ACFE-4DB8E3456D82}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3360" yWindow="3720" windowWidth="17280" windowHeight="9960" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Legend &amp; Guide" sheetId="1" r:id="rId1"/>
@@ -4580,8 +4580,8 @@
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
-      <c r="I6" s="27" t="s">
-        <v>41</v>
+      <c r="I6" s="26" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="D7" s="14">
         <f>COUNTIFS('Action Tracker'!$D$6:$D$387,$B7,'Action Tracker'!$I$6:$I$387,"Open")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="14" t="str">
         <f t="array" ref="F7:F37">_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER('Action Tracker'!F6:F243, 'Action Tracker'!F6:F243&lt;&gt;"")))</f>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="D12" s="15">
         <f>SUM(D7:D11)</f>
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F12" s="14" t="str">
         <v>C&amp;P Ceremonies Department Operating Plan</v>
@@ -12909,12 +12909,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="374220f3-34e9-48c9-8c58-31faa72ff407">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="1b1ffb37-8927-4fbe-961f-c7a3199710b9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13119,20 +13121,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="374220f3-34e9-48c9-8c58-31faa72ff407">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="1b1ffb37-8927-4fbe-961f-c7a3199710b9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F365100B-4C08-4A05-9DDA-C20D05B32AE0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{206439E8-84F1-42D1-8C84-9127261BCA0C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="1b1ffb37-8927-4fbe-961f-c7a3199710b9"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="374220f3-34e9-48c9-8c58-31faa72ff407"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -13157,18 +13166,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{206439E8-84F1-42D1-8C84-9127261BCA0C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F365100B-4C08-4A05-9DDA-C20D05B32AE0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="1b1ffb37-8927-4fbe-961f-c7a3199710b9"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="374220f3-34e9-48c9-8c58-31faa72ff407"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>